--- a/artfynd/A 51885-2024 artfynd.xlsx
+++ b/artfynd/A 51885-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>372602</v>
       </c>
       <c r="B2" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422898.98246693</v>
+        <v>422899</v>
       </c>
       <c r="R2" t="n">
-        <v>6612460.687256172</v>
+        <v>6612461</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2009-04-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-04-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,53 +777,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2707198</v>
+        <v>373620</v>
       </c>
       <c r="B3" t="n">
-        <v>95709</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100856</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>1256</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Forselles</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordbyberget, strax O, Vrm</t>
+          <t>Nordbybergets ostsluttning, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422898.98246693</v>
+        <v>422881</v>
       </c>
       <c r="R3" t="n">
-        <v>6612460.687256172</v>
+        <v>6612403</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-04-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-04-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett flertal små och stora närliggande bestånd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,62 +886,61 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Crister Albinsson, Stina Eriksson</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5044382</v>
+        <v>373644</v>
       </c>
       <c r="B4" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100856</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1256</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>Forselles</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nordbyberget, strax O, Vrm</t>
+          <t>Nordby i NV, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422942.5828214434</v>
+        <v>422915</v>
       </c>
       <c r="R4" t="n">
-        <v>6612462.317887928</v>
+        <v>6612436</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -984,22 +967,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-04-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-04-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>13 - 15 smärre bestånd längs 125 x 20 m. Ungefärlig mittkoordinat uppgiven.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +991,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Ängsgranskoghygge</t>
+          <t>Bäckravin</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1024,22 +1002,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Crister Albinsson, Stina Eriksson</t>
+          <t>Crister Albinsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2708944</v>
+        <v>632526</v>
       </c>
       <c r="B5" t="n">
-        <v>95709</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,37 +1020,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220250</v>
+        <v>2383</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nordby i NV, Vrm</t>
+          <t>Nordbybergets ostsluttning, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422892.7641047813</v>
+        <v>422881</v>
       </c>
       <c r="R5" t="n">
-        <v>6612478.515529445</v>
+        <v>6612403</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,22 +1074,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med sporkapslar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,59 +1116,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>373620</v>
+        <v>741108</v>
       </c>
       <c r="B6" t="n">
-        <v>98008</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1256</v>
+        <v>2668</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Forselles</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nordbybergets ostsluttning, Vrm</t>
+          <t>Nordby i NV, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422880.578222164</v>
+        <v>422915</v>
       </c>
       <c r="R6" t="n">
-        <v>6612403.413911848</v>
+        <v>6612436</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1227,27 +1181,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-05-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-05-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett flertal små och stora närliggande bestånd.</t>
+          <t>2012-04-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1200,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Bäckravin</t>
+          <t>Bäckstrand</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>block</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1279,15 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>632526</v>
+        <v>790131</v>
       </c>
       <c r="B7" t="n">
-        <v>92683</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,34 +1234,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2383</v>
+        <v>2813</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bågpraktmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Plagiomnium medium</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nordbybergets ostsluttning, Vrm</t>
+          <t>Nordby i NV, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422880.578222164</v>
+        <v>422915</v>
       </c>
       <c r="R7" t="n">
-        <v>6612403.413911848</v>
+        <v>6612436</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1349,27 +1288,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-05-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-05-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med sporkapslar.</t>
+          <t>2012-04-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,15 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>790131</v>
+        <v>1174375</v>
       </c>
       <c r="B8" t="n">
-        <v>93056</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,37 +1336,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2813</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nordby i NV, Vrm</t>
+          <t>Nordbybergets ostsluttning, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422915.1930990634</v>
+        <v>422821</v>
       </c>
       <c r="R8" t="n">
-        <v>6612436.078692663</v>
+        <v>6612357</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1474,21 +1402,11 @@
           <t>2012-04-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-04-24</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1500,7 +1418,22 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Bäckravin</t>
+          <t>Ängsskogssluttning mot ravin</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>grov, död hasselstam</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>12161</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1518,53 +1451,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>741108</v>
+        <v>2432356</v>
       </c>
       <c r="B9" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2668</v>
+        <v>220075</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nordby i NV, Vrm</t>
+          <t>Nordbyberget, strax O, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422915.1930990634</v>
+        <v>422899</v>
       </c>
       <c r="R9" t="n">
-        <v>6612436.078692663</v>
+        <v>6612461</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,22 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2012-04-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-04-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2012-04-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-04-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,12 +1540,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Bäckstrand</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>block</t>
+          <t>Bäckravin</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1633,22 +1551,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Crister Albinsson, Stina Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2710941</v>
+        <v>2707198</v>
       </c>
       <c r="B10" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,17 +1589,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nordby i NV, Vrm</t>
+          <t>Nordbyberget, strax O, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422915.1930990634</v>
+        <v>422899</v>
       </c>
       <c r="R10" t="n">
-        <v>6612436.078692663</v>
+        <v>6612461</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1710,22 +1623,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2012-04-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-04-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2012-04-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-04-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,69 +1653,55 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Crister Albinsson</t>
+          <t>Crister Albinsson, Stina Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>373644</v>
+        <v>2708944</v>
       </c>
       <c r="B11" t="n">
-        <v>98008</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1256</v>
+        <v>220250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Storgröe</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poa remota</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Forselles</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordby i NV, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>422915.1930990634</v>
+        <v>422893</v>
       </c>
       <c r="R11" t="n">
-        <v>6612436.078692663</v>
+        <v>6612479</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1836,27 +1725,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2012-04-24</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2012-04-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>13 - 15 smärre bestånd längs 125 x 20 m. Ungefärlig mittkoordinat uppgiven.</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,6 +1759,215 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2710941</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nordby i NV, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>422915</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6612436</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2012-04-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2012-04-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Bäckravin</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5044382</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nordbyberget, strax O, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>422943</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6612462</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2009-04-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2009-04-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Ängsgranskoghygge</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Crister Albinsson, Stina Eriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51885-2024 artfynd.xlsx
+++ b/artfynd/A 51885-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/372602</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/373620</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/373644</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/632526</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/741108</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/790131</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1174375</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2432356</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2707198</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2708944</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1861,6 +1916,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2710941</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,8 +2028,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5044382</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>